--- a/dance_registration_forms/016_dance_registration_form--dance_registration_forms.xlsx
+++ b/dance_registration_forms/016_dance_registration_form--dance_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'ballet'}</t>
+          <t>ballet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Ballet'}</t>
+          <t>Ballet</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'ballroom'}</t>
+          <t>ballroom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Ballroom'}</t>
+          <t>Ballroom</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'contemporary'}</t>
+          <t>contemporary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Contemporary'}</t>
+          <t>Contemporary</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'hip-hop'}</t>
+          <t>hip-hop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Hip-Hop'}</t>
+          <t>Hip-Hop</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'latin'}</t>
+          <t>latin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Latin'}</t>
+          <t>Latin</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'tap'}</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Tap'}</t>
+          <t>Tap</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'course'}</t>
+          <t>course</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Course'}</t>
+          <t>Course</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'academy'}</t>
+          <t>academy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Academy'}</t>
+          <t>Academy</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'contest'}</t>
+          <t>contest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Contest'}</t>
+          <t>Contest</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'festival'}</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Festival'}</t>
+          <t>Festival</t>
         </is>
       </c>
     </row>
